--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrStandardBond001.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrStandardBond001.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\ChongQingTouZi\tams\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20385" windowHeight="8520"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20388" windowHeight="8520"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,10 +44,12 @@
     <t>证券账户/通道</t>
   </si>
   <si>
-    <t>持仓券面总额</t>
-  </si>
-  <si>
-    <t>可质押券面总额</t>
+    <t>持仓券面总额/万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可质押券面总额/万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -122,7 +129,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -164,7 +171,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -199,7 +206,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -409,16 +416,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="5" width="15.625" customWidth="1"/>
-    <col min="6" max="8" width="15.625" style="5" customWidth="1"/>
-    <col min="9" max="9" width="19.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="5" width="15.6640625" customWidth="1"/>
+    <col min="6" max="8" width="15.6640625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="19.21875" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="15" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
